--- a/templates/22-stakeholder-and-raci.xlsx
+++ b/templates/22-stakeholder-and-raci.xlsx
@@ -134,7 +134,9 @@
     <xf numFmtId="0" fontId="5" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -210,6 +212,160 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <roundedCorners val="0"/>
+  <style val="13"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Stakeholder map — influence against support</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <scatterChart>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <v>Stakeholders</v>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="9"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="1F4E79"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <xVal>
+            <numRef>
+              <f>'Stakeholders'!$D$5:$D$12</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'Stakeholders'!$C$5:$C$12</f>
+            </numRef>
+          </yVal>
+        </ser>
+        <axId val="10"/>
+        <axId val="20"/>
+      </scatterChart>
+      <valAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="2.5"/>
+          <min val="-2.5"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Support:  -2 opposed  →  +2 advocate</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="low"/>
+        <crossAx val="20"/>
+      </valAx>
+      <valAx>
+        <axId val="20"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="6"/>
+          <min val="0"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Influence over the outcome</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="3600000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -703,7 +859,7 @@
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="26" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
           <t>A. Okafor</t>
@@ -735,89 +891,229 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="9" t="n"/>
-      <c r="B6" s="9" t="n"/>
-      <c r="C6" s="9" t="n"/>
-      <c r="D6" s="9" t="n"/>
-      <c r="E6" s="10">
+    <row r="6" ht="26" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>R. Mehta</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>Support Director</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="D6" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" s="8">
         <f>IF(COUNT(C6:D6)&lt;2,"",IF(AND(C6&gt;=4,D6&lt;0),"ENGAGE NOW",IF(C6&gt;=4,"KEEP CLOSE",IF(D6&lt;0,"MONITOR","INFORM"))))</f>
         <v/>
       </c>
-      <c r="F6" s="9" t="n"/>
-      <c r="G6" s="9" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="9" t="n"/>
-      <c r="B7" s="9" t="n"/>
-      <c r="C7" s="9" t="n"/>
-      <c r="D7" s="9" t="n"/>
-      <c r="E7" s="10">
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>A monthly number she can take to the exec review</t>
+        </is>
+      </c>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>Champion</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="26" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>J. Lindqvist</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>Finance Business Partner</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D7" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="8">
         <f>IF(COUNT(C7:D7)&lt;2,"",IF(AND(C7&gt;=4,D7&lt;0),"ENGAGE NOW",IF(C7&gt;=4,"KEEP CLOSE",IF(D7&lt;0,"MONITOR","INFORM"))))</f>
         <v/>
       </c>
-      <c r="F7" s="9" t="n"/>
-      <c r="G7" s="9" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="9" t="n"/>
-      <c r="B8" s="9" t="n"/>
-      <c r="C8" s="9" t="n"/>
-      <c r="D8" s="9" t="n"/>
-      <c r="E8" s="10">
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>The benefit accounting policy agreed before baseline</t>
+        </is>
+      </c>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>Black Belt</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="26" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>S. Duarte</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>WFM Lead</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" s="7" t="n">
+        <v>-2</v>
+      </c>
+      <c r="E8" s="8">
         <f>IF(COUNT(C8:D8)&lt;2,"",IF(AND(C8&gt;=4,D8&lt;0),"ENGAGE NOW",IF(C8&gt;=4,"KEEP CLOSE",IF(D8&lt;0,"MONITOR","INFORM"))))</f>
         <v/>
       </c>
-      <c r="F8" s="9" t="n"/>
-      <c r="G8" s="9" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="9" t="n"/>
-      <c r="B9" s="9" t="n"/>
-      <c r="C9" s="9" t="n"/>
-      <c r="D9" s="9" t="n"/>
-      <c r="E9" s="10">
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>Assurance the harvest is scheduled, not assumed</t>
+        </is>
+      </c>
+      <c r="G8" s="7" t="inlineStr">
+        <is>
+          <t>Champion</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="26" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>P. Nwosu</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>Platform Engineering Manager</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" s="8">
         <f>IF(COUNT(C9:D9)&lt;2,"",IF(AND(C9&gt;=4,D9&lt;0),"ENGAGE NOW",IF(C9&gt;=4,"KEEP CLOSE",IF(D9&lt;0,"MONITOR","INFORM"))))</f>
         <v/>
       </c>
-      <c r="F9" s="9" t="n"/>
-      <c r="G9" s="9" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="9" t="n"/>
-      <c r="B10" s="9" t="n"/>
-      <c r="C10" s="9" t="n"/>
-      <c r="D10" s="9" t="n"/>
-      <c r="E10" s="10">
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>A scoped ticket, not a standing request</t>
+        </is>
+      </c>
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>Black Belt</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="26" customHeight="1">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>K. Tanaka</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>QA Lead</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" s="8">
         <f>IF(COUNT(C10:D10)&lt;2,"",IF(AND(C10&gt;=4,D10&lt;0),"ENGAGE NOW",IF(C10&gt;=4,"KEEP CLOSE",IF(D10&lt;0,"MONITOR","INFORM"))))</f>
         <v/>
       </c>
-      <c r="F10" s="9" t="n"/>
-      <c r="G10" s="9" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="9" t="n"/>
-      <c r="B11" s="9" t="n"/>
-      <c r="C11" s="9" t="n"/>
-      <c r="D11" s="9" t="n"/>
-      <c r="E11" s="10">
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>Involvement in the operational definition</t>
+        </is>
+      </c>
+      <c r="G10" s="7" t="inlineStr">
+        <is>
+          <t>Black Belt</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="26" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>M. Alvarez</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>Tier 1 Team Lead</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" s="8">
         <f>IF(COUNT(C11:D11)&lt;2,"",IF(AND(C11&gt;=4,D11&lt;0),"ENGAGE NOW",IF(C11&gt;=4,"KEEP CLOSE",IF(D11&lt;0,"MONITOR","INFORM"))))</f>
         <v/>
       </c>
-      <c r="F11" s="9" t="n"/>
-      <c r="G11" s="9" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="9" t="n"/>
-      <c r="B12" s="9" t="n"/>
-      <c r="C12" s="9" t="n"/>
-      <c r="D12" s="9" t="n"/>
-      <c r="E12" s="10">
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>Her agents consulted before the process changes</t>
+        </is>
+      </c>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>Process owner</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="26" customHeight="1">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>D. Byrne</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>Compliance</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="8">
         <f>IF(COUNT(C12:D12)&lt;2,"",IF(AND(C12&gt;=4,D12&lt;0),"ENGAGE NOW",IF(C12&gt;=4,"KEEP CLOSE",IF(D12&lt;0,"MONITOR","INFORM"))))</f>
         <v/>
       </c>
-      <c r="F12" s="9" t="n"/>
-      <c r="G12" s="9" t="n"/>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>Sight of anything touching retention or consent</t>
+        </is>
+      </c>
+      <c r="G12" s="7" t="inlineStr">
+        <is>
+          <t>Champion</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="9" t="n"/>
@@ -1019,6 +1315,7 @@
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1135,62 +1432,182 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="n"/>
-      <c r="B6" s="15" t="n"/>
-      <c r="C6" s="15" t="n"/>
-      <c r="D6" s="15" t="n"/>
-      <c r="E6" s="15" t="n"/>
-      <c r="F6" s="15" t="n"/>
-      <c r="G6" s="10">
-        <f>IF(COUNTA(A6)=0,"",IF(COUNTIF(B6:F6,"A")=1,"OK",IF(COUNTIF(B6:F6,"A")=0,"NO OWNER","MORE THAN ONE")))</f>
+      <c r="A6" s="14" t="inlineStr">
+        <is>
+          <t>Agree the operational definition of a defect</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="C6" s="14" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="D6" s="14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E6" s="14" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F6" s="14" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G6" s="8">
+        <f>IF(COUNTIF(B6:F6,"A")=1,"OK",IF(COUNTIF(B6:F6,"A")=0,"NO OWNER","MORE THAN ONE"))</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="n"/>
-      <c r="B7" s="15" t="n"/>
-      <c r="C7" s="15" t="n"/>
-      <c r="D7" s="15" t="n"/>
-      <c r="E7" s="15" t="n"/>
-      <c r="F7" s="15" t="n"/>
-      <c r="G7" s="10">
-        <f>IF(COUNTA(A7)=0,"",IF(COUNTIF(B7:F7,"A")=1,"OK",IF(COUNTIF(B7:F7,"A")=0,"NO OWNER","MORE THAN ONE")))</f>
+      <c r="A7" s="14" t="inlineStr">
+        <is>
+          <t>Approve the pilot design and stopping rule</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="C7" s="14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D7" s="14" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E7" s="14" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F7" s="14" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G7" s="8">
+        <f>IF(COUNTIF(B7:F7,"A")=1,"OK",IF(COUNTIF(B7:F7,"A")=0,"NO OWNER","MORE THAN ONE"))</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="n"/>
-      <c r="B8" s="15" t="n"/>
-      <c r="C8" s="15" t="n"/>
-      <c r="D8" s="15" t="n"/>
-      <c r="E8" s="15" t="n"/>
-      <c r="F8" s="15" t="n"/>
-      <c r="G8" s="10">
-        <f>IF(COUNTA(A8)=0,"",IF(COUNTIF(B8:F8,"A")=1,"OK",IF(COUNTIF(B8:F8,"A")=0,"NO OWNER","MORE THAN ONE")))</f>
+      <c r="A8" s="14" t="inlineStr">
+        <is>
+          <t>Change the routing rules in production</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C8" s="14" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="D8" s="14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E8" s="14" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F8" s="14" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G8" s="8">
+        <f>IF(COUNTIF(B8:F8,"A")=1,"OK",IF(COUNTIF(B8:F8,"A")=0,"NO OWNER","MORE THAN ONE"))</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="n"/>
-      <c r="B9" s="15" t="n"/>
-      <c r="C9" s="15" t="n"/>
-      <c r="D9" s="15" t="n"/>
-      <c r="E9" s="15" t="n"/>
-      <c r="F9" s="15" t="n"/>
-      <c r="G9" s="10">
-        <f>IF(COUNTA(A9)=0,"",IF(COUNTIF(B9:F9,"A")=1,"OK",IF(COUNTIF(B9:F9,"A")=0,"NO OWNER","MORE THAN ONE")))</f>
+      <c r="A9" s="14" t="inlineStr">
+        <is>
+          <t>Own the control chart and its reaction plan</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C9" s="14" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="D9" s="14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E9" s="14" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F9" s="14" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G9" s="8">
+        <f>IF(COUNTIF(B9:F9,"A")=1,"OK",IF(COUNTIF(B9:F9,"A")=0,"NO OWNER","MORE THAN ONE"))</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="n"/>
-      <c r="B10" s="15" t="n"/>
-      <c r="C10" s="15" t="n"/>
-      <c r="D10" s="15" t="n"/>
-      <c r="E10" s="15" t="n"/>
-      <c r="F10" s="15" t="n"/>
-      <c r="G10" s="10">
-        <f>IF(COUNTA(A10)=0,"",IF(COUNTIF(B10:F10,"A")=1,"OK",IF(COUNTIF(B10:F10,"A")=0,"NO OWNER","MORE THAN ONE")))</f>
+      <c r="A10" s="14" t="inlineStr">
+        <is>
+          <t>Release the headcount the project frees</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="C10" s="14" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D10" s="14" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E10" s="14" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F10" s="14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G10" s="8">
+        <f>IF(COUNTIF(B10:F10,"A")=1,"OK",IF(COUNTIF(B10:F10,"A")=0,"NO OWNER","MORE THAN ONE"))</f>
         <v/>
       </c>
     </row>

--- a/templates/22-stakeholder-and-raci.xlsx
+++ b/templates/22-stakeholder-and-raci.xlsx
@@ -236,6 +236,7 @@
     </title>
     <plotArea>
       <scatterChart>
+        <scatterStyle val="lineMarker"/>
         <ser>
           <idx val="0"/>
           <order val="0"/>
@@ -268,6 +269,72 @@
           <yVal>
             <numRef>
               <f>'Stakeholders'!$C$5:$C$12</f>
+            </numRef>
+          </yVal>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <v>High influence threshold</v>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="C0392B"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <xVal>
+            <numRef>
+              <f>'Stakeholders'!$J$5:$J$12</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'Stakeholders'!$I$5:$I$12</f>
+            </numRef>
+          </yVal>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <v>Opposed / supportive threshold</v>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="C0392B"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <xVal>
+            <numRef>
+              <f>'Stakeholders'!$K$5:$K$12</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'Stakeholders'!$L$5:$L$12</f>
             </numRef>
           </yVal>
         </ser>
@@ -335,6 +402,9 @@
         <crossAx val="10"/>
       </valAx>
     </plotArea>
+    <legend>
+      <legendPos val="b"/>
+    </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
@@ -345,7 +415,7 @@
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>8</col>
+      <col>13</col>
       <colOff>0</colOff>
       <row>3</row>
       <rowOff>0</rowOff>
@@ -789,7 +859,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:L28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -799,6 +869,10 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="30" customWidth="1" min="6" max="6"/>
     <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="6" customWidth="1" min="9" max="9"/>
+    <col width="6" customWidth="1" min="10" max="10"/>
+    <col width="6" customWidth="1" min="11" max="11"/>
+    <col width="6" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -858,6 +932,11 @@
           <t>Owner</t>
         </is>
       </c>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>quadrant dividers — the chart reads these</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="26" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
@@ -890,6 +969,20 @@
           <t>Black Belt</t>
         </is>
       </c>
+      <c r="I5" s="5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J5" s="5">
+        <f>D5</f>
+        <v/>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <f>C5</f>
+        <v/>
+      </c>
     </row>
     <row r="6" ht="26" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
@@ -922,6 +1015,20 @@
           <t>Champion</t>
         </is>
       </c>
+      <c r="I6" s="5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J6" s="5">
+        <f>D6</f>
+        <v/>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="5">
+        <f>C6</f>
+        <v/>
+      </c>
     </row>
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
@@ -954,6 +1061,20 @@
           <t>Black Belt</t>
         </is>
       </c>
+      <c r="I7" s="5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J7" s="5">
+        <f>D7</f>
+        <v/>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="5">
+        <f>C7</f>
+        <v/>
+      </c>
     </row>
     <row r="8" ht="26" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
@@ -986,6 +1107,20 @@
           <t>Champion</t>
         </is>
       </c>
+      <c r="I8" s="5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J8" s="5">
+        <f>D8</f>
+        <v/>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="5">
+        <f>C8</f>
+        <v/>
+      </c>
     </row>
     <row r="9" ht="26" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
@@ -1018,6 +1153,20 @@
           <t>Black Belt</t>
         </is>
       </c>
+      <c r="I9" s="5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J9" s="5">
+        <f>D9</f>
+        <v/>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="5">
+        <f>C9</f>
+        <v/>
+      </c>
     </row>
     <row r="10" ht="26" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
@@ -1050,6 +1199,20 @@
           <t>Black Belt</t>
         </is>
       </c>
+      <c r="I10" s="5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J10" s="5">
+        <f>D10</f>
+        <v/>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="5">
+        <f>C10</f>
+        <v/>
+      </c>
     </row>
     <row r="11" ht="26" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
@@ -1082,6 +1245,20 @@
           <t>Process owner</t>
         </is>
       </c>
+      <c r="I11" s="5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J11" s="5">
+        <f>D11</f>
+        <v/>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="5">
+        <f>C11</f>
+        <v/>
+      </c>
     </row>
     <row r="12" ht="26" customHeight="1">
       <c r="A12" s="7" t="inlineStr">
@@ -1113,6 +1290,20 @@
         <is>
           <t>Champion</t>
         </is>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J12" s="5">
+        <f>D12</f>
+        <v/>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="5">
+        <f>C12</f>
+        <v/>
       </c>
     </row>
     <row r="13">

--- a/templates/22-stakeholder-and-raci.xlsx
+++ b/templates/22-stakeholder-and-raci.xlsx
@@ -296,12 +296,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'Stakeholders'!$J$5:$J$12</f>
+              <f>'Stakeholders'!$I$5:$I$6</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'Stakeholders'!$I$5:$I$12</f>
+              <f>'Stakeholders'!$J$5:$J$6</f>
             </numRef>
           </yVal>
         </ser>
@@ -329,12 +329,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'Stakeholders'!$K$5:$K$12</f>
+              <f>'Stakeholders'!$K$5:$K$6</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'Stakeholders'!$L$5:$L$12</f>
+              <f>'Stakeholders'!$L$5:$L$6</f>
             </numRef>
           </yVal>
         </ser>
@@ -970,18 +970,16 @@
         </is>
       </c>
       <c r="I5" s="5" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="J5" s="5" t="n">
         <v>3.5</v>
-      </c>
-      <c r="J5" s="5">
-        <f>D5</f>
-        <v/>
       </c>
       <c r="K5" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="L5" s="5">
-        <f>C5</f>
-        <v/>
+      <c r="L5" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6" ht="26" customHeight="1">
@@ -1016,18 +1014,16 @@
         </is>
       </c>
       <c r="I6" s="5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J6" s="5" t="n">
         <v>3.5</v>
-      </c>
-      <c r="J6" s="5">
-        <f>D6</f>
-        <v/>
       </c>
       <c r="K6" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="L6" s="5">
-        <f>C6</f>
-        <v/>
+      <c r="L6" s="5" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="7" ht="26" customHeight="1">
@@ -1061,20 +1057,6 @@
           <t>Black Belt</t>
         </is>
       </c>
-      <c r="I7" s="5" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="J7" s="5">
-        <f>D7</f>
-        <v/>
-      </c>
-      <c r="K7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" s="5">
-        <f>C7</f>
-        <v/>
-      </c>
     </row>
     <row r="8" ht="26" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
@@ -1107,20 +1089,6 @@
           <t>Champion</t>
         </is>
       </c>
-      <c r="I8" s="5" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="J8" s="5">
-        <f>D8</f>
-        <v/>
-      </c>
-      <c r="K8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" s="5">
-        <f>C8</f>
-        <v/>
-      </c>
     </row>
     <row r="9" ht="26" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
@@ -1153,20 +1121,6 @@
           <t>Black Belt</t>
         </is>
       </c>
-      <c r="I9" s="5" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="J9" s="5">
-        <f>D9</f>
-        <v/>
-      </c>
-      <c r="K9" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" s="5">
-        <f>C9</f>
-        <v/>
-      </c>
     </row>
     <row r="10" ht="26" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
@@ -1199,20 +1153,6 @@
           <t>Black Belt</t>
         </is>
       </c>
-      <c r="I10" s="5" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="J10" s="5">
-        <f>D10</f>
-        <v/>
-      </c>
-      <c r="K10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" s="5">
-        <f>C10</f>
-        <v/>
-      </c>
     </row>
     <row r="11" ht="26" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
@@ -1245,20 +1185,6 @@
           <t>Process owner</t>
         </is>
       </c>
-      <c r="I11" s="5" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="J11" s="5">
-        <f>D11</f>
-        <v/>
-      </c>
-      <c r="K11" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" s="5">
-        <f>C11</f>
-        <v/>
-      </c>
     </row>
     <row r="12" ht="26" customHeight="1">
       <c r="A12" s="7" t="inlineStr">
@@ -1290,20 +1216,6 @@
         <is>
           <t>Champion</t>
         </is>
-      </c>
-      <c r="I12" s="5" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="J12" s="5">
-        <f>D12</f>
-        <v/>
-      </c>
-      <c r="K12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" s="5">
-        <f>C12</f>
-        <v/>
       </c>
     </row>
     <row r="13">

--- a/templates/22-stakeholder-and-raci.xlsx
+++ b/templates/22-stakeholder-and-raci.xlsx
@@ -417,7 +417,7 @@
     <from>
       <col>13</col>
       <colOff>0</colOff>
-      <row>3</row>
+      <row>2</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5400000" cy="3600000"/>
@@ -1350,6 +1350,7 @@
       <c r="F23" s="9" t="n"/>
       <c r="G23" s="9" t="n"/>
     </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" s="11" t="inlineStr">
         <is>

--- a/templates/22-stakeholder-and-raci.xlsx
+++ b/templates/22-stakeholder-and-raci.xlsx
@@ -109,7 +109,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -134,6 +134,9 @@
     <xf numFmtId="0" fontId="5" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1461,7 +1464,13 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
+    <row r="3" ht="24" customHeight="1">
+      <c r="A3" s="14" t="inlineStr">
+        <is>
+          <t>Key: Black Belt = the person running the project day to day · Champion = the executive who owns the problem and clears the obstacles · WFM = Workforce Management, the team that owns schedules and headcount</t>
+        </is>
+      </c>
+    </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -1500,32 +1509,32 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="14" t="inlineStr">
+      <c r="A5" s="15" t="inlineStr">
         <is>
           <t>Sign the benefit and harvest mechanism</t>
         </is>
       </c>
-      <c r="B5" s="14" t="inlineStr">
+      <c r="B5" s="15" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="C5" s="14" t="inlineStr">
+      <c r="C5" s="15" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="D5" s="14" t="inlineStr">
+      <c r="D5" s="15" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="E5" s="14" t="inlineStr">
+      <c r="E5" s="15" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="F5" s="14" t="inlineStr">
+      <c r="F5" s="15" t="inlineStr">
         <is>
           <t>R</t>
         </is>
@@ -1536,32 +1545,32 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="14" t="inlineStr">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>Agree the operational definition of a defect</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B6" s="15" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="C6" s="14" t="inlineStr">
+      <c r="C6" s="15" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="D6" s="14" t="inlineStr">
+      <c r="D6" s="15" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="E6" s="14" t="inlineStr">
+      <c r="E6" s="15" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="F6" s="14" t="inlineStr">
+      <c r="F6" s="15" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -1572,32 +1581,32 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="14" t="inlineStr">
+      <c r="A7" s="15" t="inlineStr">
         <is>
           <t>Approve the pilot design and stopping rule</t>
         </is>
       </c>
-      <c r="B7" s="14" t="inlineStr">
+      <c r="B7" s="15" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="C7" s="14" t="inlineStr">
+      <c r="C7" s="15" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="D7" s="14" t="inlineStr">
+      <c r="D7" s="15" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="E7" s="14" t="inlineStr">
+      <c r="E7" s="15" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="F7" s="14" t="inlineStr">
+      <c r="F7" s="15" t="inlineStr">
         <is>
           <t>I</t>
         </is>
@@ -1608,32 +1617,32 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="14" t="inlineStr">
+      <c r="A8" s="15" t="inlineStr">
         <is>
           <t>Change the routing rules in production</t>
         </is>
       </c>
-      <c r="B8" s="14" t="inlineStr">
+      <c r="B8" s="15" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="C8" s="14" t="inlineStr">
+      <c r="C8" s="15" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="D8" s="14" t="inlineStr">
+      <c r="D8" s="15" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="E8" s="14" t="inlineStr">
+      <c r="E8" s="15" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="F8" s="14" t="inlineStr">
+      <c r="F8" s="15" t="inlineStr">
         <is>
           <t>I</t>
         </is>
@@ -1644,32 +1653,32 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="14" t="inlineStr">
+      <c r="A9" s="15" t="inlineStr">
         <is>
           <t>Own the control chart and its reaction plan</t>
         </is>
       </c>
-      <c r="B9" s="14" t="inlineStr">
+      <c r="B9" s="15" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="C9" s="14" t="inlineStr">
+      <c r="C9" s="15" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="D9" s="14" t="inlineStr">
+      <c r="D9" s="15" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="E9" s="14" t="inlineStr">
+      <c r="E9" s="15" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="F9" s="14" t="inlineStr">
+      <c r="F9" s="15" t="inlineStr">
         <is>
           <t>I</t>
         </is>
@@ -1680,32 +1689,32 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="14" t="inlineStr">
+      <c r="A10" s="15" t="inlineStr">
         <is>
           <t>Release the headcount the project frees</t>
         </is>
       </c>
-      <c r="B10" s="14" t="inlineStr">
+      <c r="B10" s="15" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="C10" s="14" t="inlineStr">
+      <c r="C10" s="15" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D10" s="14" t="inlineStr">
+      <c r="D10" s="15" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="E10" s="14" t="inlineStr">
+      <c r="E10" s="15" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="F10" s="14" t="inlineStr">
+      <c r="F10" s="15" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -1716,137 +1725,138 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="15" t="n"/>
-      <c r="B11" s="15" t="n"/>
-      <c r="C11" s="15" t="n"/>
-      <c r="D11" s="15" t="n"/>
-      <c r="E11" s="15" t="n"/>
-      <c r="F11" s="15" t="n"/>
+      <c r="A11" s="16" t="n"/>
+      <c r="B11" s="16" t="n"/>
+      <c r="C11" s="16" t="n"/>
+      <c r="D11" s="16" t="n"/>
+      <c r="E11" s="16" t="n"/>
+      <c r="F11" s="16" t="n"/>
       <c r="G11" s="10">
         <f>IF(COUNTA(A11)=0,"",IF(COUNTIF(B11:F11,"A")=1,"OK",IF(COUNTIF(B11:F11,"A")=0,"NO OWNER","MORE THAN ONE")))</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="n"/>
-      <c r="B12" s="15" t="n"/>
-      <c r="C12" s="15" t="n"/>
-      <c r="D12" s="15" t="n"/>
-      <c r="E12" s="15" t="n"/>
-      <c r="F12" s="15" t="n"/>
+      <c r="A12" s="16" t="n"/>
+      <c r="B12" s="16" t="n"/>
+      <c r="C12" s="16" t="n"/>
+      <c r="D12" s="16" t="n"/>
+      <c r="E12" s="16" t="n"/>
+      <c r="F12" s="16" t="n"/>
       <c r="G12" s="10">
         <f>IF(COUNTA(A12)=0,"",IF(COUNTIF(B12:F12,"A")=1,"OK",IF(COUNTIF(B12:F12,"A")=0,"NO OWNER","MORE THAN ONE")))</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="n"/>
-      <c r="B13" s="15" t="n"/>
-      <c r="C13" s="15" t="n"/>
-      <c r="D13" s="15" t="n"/>
-      <c r="E13" s="15" t="n"/>
-      <c r="F13" s="15" t="n"/>
+      <c r="A13" s="16" t="n"/>
+      <c r="B13" s="16" t="n"/>
+      <c r="C13" s="16" t="n"/>
+      <c r="D13" s="16" t="n"/>
+      <c r="E13" s="16" t="n"/>
+      <c r="F13" s="16" t="n"/>
       <c r="G13" s="10">
         <f>IF(COUNTA(A13)=0,"",IF(COUNTIF(B13:F13,"A")=1,"OK",IF(COUNTIF(B13:F13,"A")=0,"NO OWNER","MORE THAN ONE")))</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="15" t="n"/>
-      <c r="B14" s="15" t="n"/>
-      <c r="C14" s="15" t="n"/>
-      <c r="D14" s="15" t="n"/>
-      <c r="E14" s="15" t="n"/>
-      <c r="F14" s="15" t="n"/>
+      <c r="A14" s="16" t="n"/>
+      <c r="B14" s="16" t="n"/>
+      <c r="C14" s="16" t="n"/>
+      <c r="D14" s="16" t="n"/>
+      <c r="E14" s="16" t="n"/>
+      <c r="F14" s="16" t="n"/>
       <c r="G14" s="10">
         <f>IF(COUNTA(A14)=0,"",IF(COUNTIF(B14:F14,"A")=1,"OK",IF(COUNTIF(B14:F14,"A")=0,"NO OWNER","MORE THAN ONE")))</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="15" t="n"/>
-      <c r="B15" s="15" t="n"/>
-      <c r="C15" s="15" t="n"/>
-      <c r="D15" s="15" t="n"/>
-      <c r="E15" s="15" t="n"/>
-      <c r="F15" s="15" t="n"/>
+      <c r="A15" s="16" t="n"/>
+      <c r="B15" s="16" t="n"/>
+      <c r="C15" s="16" t="n"/>
+      <c r="D15" s="16" t="n"/>
+      <c r="E15" s="16" t="n"/>
+      <c r="F15" s="16" t="n"/>
       <c r="G15" s="10">
         <f>IF(COUNTA(A15)=0,"",IF(COUNTIF(B15:F15,"A")=1,"OK",IF(COUNTIF(B15:F15,"A")=0,"NO OWNER","MORE THAN ONE")))</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="15" t="n"/>
-      <c r="B16" s="15" t="n"/>
-      <c r="C16" s="15" t="n"/>
-      <c r="D16" s="15" t="n"/>
-      <c r="E16" s="15" t="n"/>
-      <c r="F16" s="15" t="n"/>
+      <c r="A16" s="16" t="n"/>
+      <c r="B16" s="16" t="n"/>
+      <c r="C16" s="16" t="n"/>
+      <c r="D16" s="16" t="n"/>
+      <c r="E16" s="16" t="n"/>
+      <c r="F16" s="16" t="n"/>
       <c r="G16" s="10">
         <f>IF(COUNTA(A16)=0,"",IF(COUNTIF(B16:F16,"A")=1,"OK",IF(COUNTIF(B16:F16,"A")=0,"NO OWNER","MORE THAN ONE")))</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="n"/>
-      <c r="B17" s="15" t="n"/>
-      <c r="C17" s="15" t="n"/>
-      <c r="D17" s="15" t="n"/>
-      <c r="E17" s="15" t="n"/>
-      <c r="F17" s="15" t="n"/>
+      <c r="A17" s="16" t="n"/>
+      <c r="B17" s="16" t="n"/>
+      <c r="C17" s="16" t="n"/>
+      <c r="D17" s="16" t="n"/>
+      <c r="E17" s="16" t="n"/>
+      <c r="F17" s="16" t="n"/>
       <c r="G17" s="10">
         <f>IF(COUNTA(A17)=0,"",IF(COUNTIF(B17:F17,"A")=1,"OK",IF(COUNTIF(B17:F17,"A")=0,"NO OWNER","MORE THAN ONE")))</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="15" t="n"/>
-      <c r="B18" s="15" t="n"/>
-      <c r="C18" s="15" t="n"/>
-      <c r="D18" s="15" t="n"/>
-      <c r="E18" s="15" t="n"/>
-      <c r="F18" s="15" t="n"/>
+      <c r="A18" s="16" t="n"/>
+      <c r="B18" s="16" t="n"/>
+      <c r="C18" s="16" t="n"/>
+      <c r="D18" s="16" t="n"/>
+      <c r="E18" s="16" t="n"/>
+      <c r="F18" s="16" t="n"/>
       <c r="G18" s="10">
         <f>IF(COUNTA(A18)=0,"",IF(COUNTIF(B18:F18,"A")=1,"OK",IF(COUNTIF(B18:F18,"A")=0,"NO OWNER","MORE THAN ONE")))</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="15" t="n"/>
-      <c r="B19" s="15" t="n"/>
-      <c r="C19" s="15" t="n"/>
-      <c r="D19" s="15" t="n"/>
-      <c r="E19" s="15" t="n"/>
-      <c r="F19" s="15" t="n"/>
+      <c r="A19" s="16" t="n"/>
+      <c r="B19" s="16" t="n"/>
+      <c r="C19" s="16" t="n"/>
+      <c r="D19" s="16" t="n"/>
+      <c r="E19" s="16" t="n"/>
+      <c r="F19" s="16" t="n"/>
       <c r="G19" s="10">
         <f>IF(COUNTA(A19)=0,"",IF(COUNTIF(B19:F19,"A")=1,"OK",IF(COUNTIF(B19:F19,"A")=0,"NO OWNER","MORE THAN ONE")))</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="15" t="n"/>
-      <c r="B20" s="15" t="n"/>
-      <c r="C20" s="15" t="n"/>
-      <c r="D20" s="15" t="n"/>
-      <c r="E20" s="15" t="n"/>
-      <c r="F20" s="15" t="n"/>
+      <c r="A20" s="16" t="n"/>
+      <c r="B20" s="16" t="n"/>
+      <c r="C20" s="16" t="n"/>
+      <c r="D20" s="16" t="n"/>
+      <c r="E20" s="16" t="n"/>
+      <c r="F20" s="16" t="n"/>
       <c r="G20" s="10">
         <f>IF(COUNTA(A20)=0,"",IF(COUNTIF(B20:F20,"A")=1,"OK",IF(COUNTIF(B20:F20,"A")=0,"NO OWNER","MORE THAN ONE")))</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="15" t="n"/>
-      <c r="B21" s="15" t="n"/>
-      <c r="C21" s="15" t="n"/>
-      <c r="D21" s="15" t="n"/>
-      <c r="E21" s="15" t="n"/>
-      <c r="F21" s="15" t="n"/>
+      <c r="A21" s="16" t="n"/>
+      <c r="B21" s="16" t="n"/>
+      <c r="C21" s="16" t="n"/>
+      <c r="D21" s="16" t="n"/>
+      <c r="E21" s="16" t="n"/>
+      <c r="F21" s="16" t="n"/>
       <c r="G21" s="10">
         <f>IF(COUNTA(A21)=0,"",IF(COUNTIF(B21:F21,"A")=1,"OK",IF(COUNTIF(B21:F21,"A")=0,"NO OWNER","MORE THAN ONE")))</f>
         <v/>
       </c>
     </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
@@ -1855,7 +1865,8 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
+    <mergeCell ref="A3:G3"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A23:G23"/>

--- a/templates/22-stakeholder-and-raci.xlsx
+++ b/templates/22-stakeholder-and-raci.xlsx
@@ -769,14 +769,14 @@
     <row r="6">
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>Green row</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
+          <t>Green cells</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>A worked example so you can see the expected format. Delete it when you start.</t>
+          <t>A worked example, so you can see the expected format and the charts say something the moment you open the file. Replace it with your own data when you start.</t>
         </is>
       </c>
     </row>

--- a/templates/22-stakeholder-and-raci.xlsx
+++ b/templates/22-stakeholder-and-raci.xlsx
@@ -109,7 +109,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -126,11 +126,10 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1226,7 +1225,7 @@
       <c r="B13" s="9" t="n"/>
       <c r="C13" s="9" t="n"/>
       <c r="D13" s="9" t="n"/>
-      <c r="E13" s="10">
+      <c r="E13" s="8">
         <f>IF(COUNT(C13:D13)&lt;2,"",IF(AND(C13&gt;=4,D13&lt;0),"ENGAGE NOW",IF(C13&gt;=4,"KEEP CLOSE",IF(D13&lt;0,"MONITOR","INFORM"))))</f>
         <v/>
       </c>
@@ -1238,7 +1237,7 @@
       <c r="B14" s="9" t="n"/>
       <c r="C14" s="9" t="n"/>
       <c r="D14" s="9" t="n"/>
-      <c r="E14" s="10">
+      <c r="E14" s="8">
         <f>IF(COUNT(C14:D14)&lt;2,"",IF(AND(C14&gt;=4,D14&lt;0),"ENGAGE NOW",IF(C14&gt;=4,"KEEP CLOSE",IF(D14&lt;0,"MONITOR","INFORM"))))</f>
         <v/>
       </c>
@@ -1250,7 +1249,7 @@
       <c r="B15" s="9" t="n"/>
       <c r="C15" s="9" t="n"/>
       <c r="D15" s="9" t="n"/>
-      <c r="E15" s="10">
+      <c r="E15" s="8">
         <f>IF(COUNT(C15:D15)&lt;2,"",IF(AND(C15&gt;=4,D15&lt;0),"ENGAGE NOW",IF(C15&gt;=4,"KEEP CLOSE",IF(D15&lt;0,"MONITOR","INFORM"))))</f>
         <v/>
       </c>
@@ -1262,7 +1261,7 @@
       <c r="B16" s="9" t="n"/>
       <c r="C16" s="9" t="n"/>
       <c r="D16" s="9" t="n"/>
-      <c r="E16" s="10">
+      <c r="E16" s="8">
         <f>IF(COUNT(C16:D16)&lt;2,"",IF(AND(C16&gt;=4,D16&lt;0),"ENGAGE NOW",IF(C16&gt;=4,"KEEP CLOSE",IF(D16&lt;0,"MONITOR","INFORM"))))</f>
         <v/>
       </c>
@@ -1274,7 +1273,7 @@
       <c r="B17" s="9" t="n"/>
       <c r="C17" s="9" t="n"/>
       <c r="D17" s="9" t="n"/>
-      <c r="E17" s="10">
+      <c r="E17" s="8">
         <f>IF(COUNT(C17:D17)&lt;2,"",IF(AND(C17&gt;=4,D17&lt;0),"ENGAGE NOW",IF(C17&gt;=4,"KEEP CLOSE",IF(D17&lt;0,"MONITOR","INFORM"))))</f>
         <v/>
       </c>
@@ -1286,7 +1285,7 @@
       <c r="B18" s="9" t="n"/>
       <c r="C18" s="9" t="n"/>
       <c r="D18" s="9" t="n"/>
-      <c r="E18" s="10">
+      <c r="E18" s="8">
         <f>IF(COUNT(C18:D18)&lt;2,"",IF(AND(C18&gt;=4,D18&lt;0),"ENGAGE NOW",IF(C18&gt;=4,"KEEP CLOSE",IF(D18&lt;0,"MONITOR","INFORM"))))</f>
         <v/>
       </c>
@@ -1298,7 +1297,7 @@
       <c r="B19" s="9" t="n"/>
       <c r="C19" s="9" t="n"/>
       <c r="D19" s="9" t="n"/>
-      <c r="E19" s="10">
+      <c r="E19" s="8">
         <f>IF(COUNT(C19:D19)&lt;2,"",IF(AND(C19&gt;=4,D19&lt;0),"ENGAGE NOW",IF(C19&gt;=4,"KEEP CLOSE",IF(D19&lt;0,"MONITOR","INFORM"))))</f>
         <v/>
       </c>
@@ -1310,7 +1309,7 @@
       <c r="B20" s="9" t="n"/>
       <c r="C20" s="9" t="n"/>
       <c r="D20" s="9" t="n"/>
-      <c r="E20" s="10">
+      <c r="E20" s="8">
         <f>IF(COUNT(C20:D20)&lt;2,"",IF(AND(C20&gt;=4,D20&lt;0),"ENGAGE NOW",IF(C20&gt;=4,"KEEP CLOSE",IF(D20&lt;0,"MONITOR","INFORM"))))</f>
         <v/>
       </c>
@@ -1322,7 +1321,7 @@
       <c r="B21" s="9" t="n"/>
       <c r="C21" s="9" t="n"/>
       <c r="D21" s="9" t="n"/>
-      <c r="E21" s="10">
+      <c r="E21" s="8">
         <f>IF(COUNT(C21:D21)&lt;2,"",IF(AND(C21&gt;=4,D21&lt;0),"ENGAGE NOW",IF(C21&gt;=4,"KEEP CLOSE",IF(D21&lt;0,"MONITOR","INFORM"))))</f>
         <v/>
       </c>
@@ -1334,7 +1333,7 @@
       <c r="B22" s="9" t="n"/>
       <c r="C22" s="9" t="n"/>
       <c r="D22" s="9" t="n"/>
-      <c r="E22" s="10">
+      <c r="E22" s="8">
         <f>IF(COUNT(C22:D22)&lt;2,"",IF(AND(C22&gt;=4,D22&lt;0),"ENGAGE NOW",IF(C22&gt;=4,"KEEP CLOSE",IF(D22&lt;0,"MONITOR","INFORM"))))</f>
         <v/>
       </c>
@@ -1346,7 +1345,7 @@
       <c r="B23" s="9" t="n"/>
       <c r="C23" s="9" t="n"/>
       <c r="D23" s="9" t="n"/>
-      <c r="E23" s="10">
+      <c r="E23" s="8">
         <f>IF(COUNT(C23:D23)&lt;2,"",IF(AND(C23&gt;=4,D23&lt;0),"ENGAGE NOW",IF(C23&gt;=4,"KEEP CLOSE",IF(D23&lt;0,"MONITOR","INFORM"))))</f>
         <v/>
       </c>
@@ -1355,47 +1354,47 @@
     </row>
     <row r="24"/>
     <row r="25">
-      <c r="A25" s="11" t="inlineStr">
+      <c r="A25" s="10" t="inlineStr">
         <is>
           <t>SUMMARY</t>
         </is>
       </c>
-      <c r="B25" s="12" t="n"/>
-      <c r="C25" s="12" t="n"/>
-      <c r="D25" s="12" t="n"/>
-      <c r="E25" s="12" t="n"/>
-      <c r="F25" s="12" t="n"/>
-      <c r="G25" s="12" t="n"/>
+      <c r="B25" s="11" t="n"/>
+      <c r="C25" s="11" t="n"/>
+      <c r="D25" s="11" t="n"/>
+      <c r="E25" s="11" t="n"/>
+      <c r="F25" s="11" t="n"/>
+      <c r="G25" s="11" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="13" t="inlineStr">
+      <c r="A26" s="12" t="inlineStr">
         <is>
           <t>Stakeholders mapped</t>
         </is>
       </c>
-      <c r="E26" s="10">
+      <c r="E26" s="8">
         <f>COUNTA(A5:A23)</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="13" t="inlineStr">
+      <c r="A27" s="12" t="inlineStr">
         <is>
           <t>High influence and opposed — deal with these first</t>
         </is>
       </c>
-      <c r="E27" s="10">
+      <c r="E27" s="8">
         <f>COUNTIF(E5:E23,"ENGAGE NOW")</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="13" t="inlineStr">
+      <c r="A28" s="12" t="inlineStr">
         <is>
           <t>High influence and supportive — your sponsors</t>
         </is>
       </c>
-      <c r="E28" s="10">
+      <c r="E28" s="8">
         <f>COUNTIF(E5:E23,"KEEP CLOSE")</f>
         <v/>
       </c>
@@ -1465,7 +1464,7 @@
       </c>
     </row>
     <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="14" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>Key: Black Belt = the person running the project day to day · Champion = the executive who owns the problem and clears the obstacles · WFM = Workforce Management, the team that owns schedules and headcount</t>
         </is>
@@ -1509,32 +1508,32 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>Sign the benefit and harvest mechanism</t>
         </is>
       </c>
-      <c r="B5" s="15" t="inlineStr">
+      <c r="B5" s="14" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="C5" s="15" t="inlineStr">
+      <c r="C5" s="14" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="D5" s="15" t="inlineStr">
+      <c r="D5" s="14" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="E5" s="15" t="inlineStr">
+      <c r="E5" s="14" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="F5" s="15" t="inlineStr">
+      <c r="F5" s="14" t="inlineStr">
         <is>
           <t>R</t>
         </is>
@@ -1545,32 +1544,32 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>Agree the operational definition of a defect</t>
         </is>
       </c>
-      <c r="B6" s="15" t="inlineStr">
+      <c r="B6" s="14" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="C6" s="15" t="inlineStr">
+      <c r="C6" s="14" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="D6" s="15" t="inlineStr">
+      <c r="D6" s="14" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="E6" s="15" t="inlineStr">
+      <c r="E6" s="14" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="F6" s="15" t="inlineStr">
+      <c r="F6" s="14" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -1581,32 +1580,32 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>Approve the pilot design and stopping rule</t>
         </is>
       </c>
-      <c r="B7" s="15" t="inlineStr">
+      <c r="B7" s="14" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="C7" s="15" t="inlineStr">
+      <c r="C7" s="14" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="D7" s="15" t="inlineStr">
+      <c r="D7" s="14" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="E7" s="15" t="inlineStr">
+      <c r="E7" s="14" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="F7" s="15" t="inlineStr">
+      <c r="F7" s="14" t="inlineStr">
         <is>
           <t>I</t>
         </is>
@@ -1617,32 +1616,32 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>Change the routing rules in production</t>
         </is>
       </c>
-      <c r="B8" s="15" t="inlineStr">
+      <c r="B8" s="14" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="C8" s="15" t="inlineStr">
+      <c r="C8" s="14" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="D8" s="15" t="inlineStr">
+      <c r="D8" s="14" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="E8" s="15" t="inlineStr">
+      <c r="E8" s="14" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="F8" s="15" t="inlineStr">
+      <c r="F8" s="14" t="inlineStr">
         <is>
           <t>I</t>
         </is>
@@ -1653,32 +1652,32 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>Own the control chart and its reaction plan</t>
         </is>
       </c>
-      <c r="B9" s="15" t="inlineStr">
+      <c r="B9" s="14" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="C9" s="15" t="inlineStr">
+      <c r="C9" s="14" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="D9" s="15" t="inlineStr">
+      <c r="D9" s="14" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="E9" s="15" t="inlineStr">
+      <c r="E9" s="14" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="F9" s="15" t="inlineStr">
+      <c r="F9" s="14" t="inlineStr">
         <is>
           <t>I</t>
         </is>
@@ -1689,32 +1688,32 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="A10" s="14" t="inlineStr">
         <is>
           <t>Release the headcount the project frees</t>
         </is>
       </c>
-      <c r="B10" s="15" t="inlineStr">
+      <c r="B10" s="14" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="C10" s="15" t="inlineStr">
+      <c r="C10" s="14" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D10" s="15" t="inlineStr">
+      <c r="D10" s="14" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="E10" s="15" t="inlineStr">
+      <c r="E10" s="14" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="F10" s="15" t="inlineStr">
+      <c r="F10" s="14" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -1725,133 +1724,133 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="16" t="n"/>
-      <c r="B11" s="16" t="n"/>
-      <c r="C11" s="16" t="n"/>
-      <c r="D11" s="16" t="n"/>
-      <c r="E11" s="16" t="n"/>
-      <c r="F11" s="16" t="n"/>
-      <c r="G11" s="10">
+      <c r="A11" s="15" t="n"/>
+      <c r="B11" s="15" t="n"/>
+      <c r="C11" s="15" t="n"/>
+      <c r="D11" s="15" t="n"/>
+      <c r="E11" s="15" t="n"/>
+      <c r="F11" s="15" t="n"/>
+      <c r="G11" s="8">
         <f>IF(COUNTA(A11)=0,"",IF(COUNTIF(B11:F11,"A")=1,"OK",IF(COUNTIF(B11:F11,"A")=0,"NO OWNER","MORE THAN ONE")))</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="16" t="n"/>
-      <c r="B12" s="16" t="n"/>
-      <c r="C12" s="16" t="n"/>
-      <c r="D12" s="16" t="n"/>
-      <c r="E12" s="16" t="n"/>
-      <c r="F12" s="16" t="n"/>
-      <c r="G12" s="10">
+      <c r="A12" s="15" t="n"/>
+      <c r="B12" s="15" t="n"/>
+      <c r="C12" s="15" t="n"/>
+      <c r="D12" s="15" t="n"/>
+      <c r="E12" s="15" t="n"/>
+      <c r="F12" s="15" t="n"/>
+      <c r="G12" s="8">
         <f>IF(COUNTA(A12)=0,"",IF(COUNTIF(B12:F12,"A")=1,"OK",IF(COUNTIF(B12:F12,"A")=0,"NO OWNER","MORE THAN ONE")))</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="16" t="n"/>
-      <c r="B13" s="16" t="n"/>
-      <c r="C13" s="16" t="n"/>
-      <c r="D13" s="16" t="n"/>
-      <c r="E13" s="16" t="n"/>
-      <c r="F13" s="16" t="n"/>
-      <c r="G13" s="10">
+      <c r="A13" s="15" t="n"/>
+      <c r="B13" s="15" t="n"/>
+      <c r="C13" s="15" t="n"/>
+      <c r="D13" s="15" t="n"/>
+      <c r="E13" s="15" t="n"/>
+      <c r="F13" s="15" t="n"/>
+      <c r="G13" s="8">
         <f>IF(COUNTA(A13)=0,"",IF(COUNTIF(B13:F13,"A")=1,"OK",IF(COUNTIF(B13:F13,"A")=0,"NO OWNER","MORE THAN ONE")))</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="16" t="n"/>
-      <c r="B14" s="16" t="n"/>
-      <c r="C14" s="16" t="n"/>
-      <c r="D14" s="16" t="n"/>
-      <c r="E14" s="16" t="n"/>
-      <c r="F14" s="16" t="n"/>
-      <c r="G14" s="10">
+      <c r="A14" s="15" t="n"/>
+      <c r="B14" s="15" t="n"/>
+      <c r="C14" s="15" t="n"/>
+      <c r="D14" s="15" t="n"/>
+      <c r="E14" s="15" t="n"/>
+      <c r="F14" s="15" t="n"/>
+      <c r="G14" s="8">
         <f>IF(COUNTA(A14)=0,"",IF(COUNTIF(B14:F14,"A")=1,"OK",IF(COUNTIF(B14:F14,"A")=0,"NO OWNER","MORE THAN ONE")))</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="16" t="n"/>
-      <c r="B15" s="16" t="n"/>
-      <c r="C15" s="16" t="n"/>
-      <c r="D15" s="16" t="n"/>
-      <c r="E15" s="16" t="n"/>
-      <c r="F15" s="16" t="n"/>
-      <c r="G15" s="10">
+      <c r="A15" s="15" t="n"/>
+      <c r="B15" s="15" t="n"/>
+      <c r="C15" s="15" t="n"/>
+      <c r="D15" s="15" t="n"/>
+      <c r="E15" s="15" t="n"/>
+      <c r="F15" s="15" t="n"/>
+      <c r="G15" s="8">
         <f>IF(COUNTA(A15)=0,"",IF(COUNTIF(B15:F15,"A")=1,"OK",IF(COUNTIF(B15:F15,"A")=0,"NO OWNER","MORE THAN ONE")))</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="16" t="n"/>
-      <c r="B16" s="16" t="n"/>
-      <c r="C16" s="16" t="n"/>
-      <c r="D16" s="16" t="n"/>
-      <c r="E16" s="16" t="n"/>
-      <c r="F16" s="16" t="n"/>
-      <c r="G16" s="10">
+      <c r="A16" s="15" t="n"/>
+      <c r="B16" s="15" t="n"/>
+      <c r="C16" s="15" t="n"/>
+      <c r="D16" s="15" t="n"/>
+      <c r="E16" s="15" t="n"/>
+      <c r="F16" s="15" t="n"/>
+      <c r="G16" s="8">
         <f>IF(COUNTA(A16)=0,"",IF(COUNTIF(B16:F16,"A")=1,"OK",IF(COUNTIF(B16:F16,"A")=0,"NO OWNER","MORE THAN ONE")))</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="16" t="n"/>
-      <c r="B17" s="16" t="n"/>
-      <c r="C17" s="16" t="n"/>
-      <c r="D17" s="16" t="n"/>
-      <c r="E17" s="16" t="n"/>
-      <c r="F17" s="16" t="n"/>
-      <c r="G17" s="10">
+      <c r="A17" s="15" t="n"/>
+      <c r="B17" s="15" t="n"/>
+      <c r="C17" s="15" t="n"/>
+      <c r="D17" s="15" t="n"/>
+      <c r="E17" s="15" t="n"/>
+      <c r="F17" s="15" t="n"/>
+      <c r="G17" s="8">
         <f>IF(COUNTA(A17)=0,"",IF(COUNTIF(B17:F17,"A")=1,"OK",IF(COUNTIF(B17:F17,"A")=0,"NO OWNER","MORE THAN ONE")))</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="16" t="n"/>
-      <c r="B18" s="16" t="n"/>
-      <c r="C18" s="16" t="n"/>
-      <c r="D18" s="16" t="n"/>
-      <c r="E18" s="16" t="n"/>
-      <c r="F18" s="16" t="n"/>
-      <c r="G18" s="10">
+      <c r="A18" s="15" t="n"/>
+      <c r="B18" s="15" t="n"/>
+      <c r="C18" s="15" t="n"/>
+      <c r="D18" s="15" t="n"/>
+      <c r="E18" s="15" t="n"/>
+      <c r="F18" s="15" t="n"/>
+      <c r="G18" s="8">
         <f>IF(COUNTA(A18)=0,"",IF(COUNTIF(B18:F18,"A")=1,"OK",IF(COUNTIF(B18:F18,"A")=0,"NO OWNER","MORE THAN ONE")))</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="16" t="n"/>
-      <c r="B19" s="16" t="n"/>
-      <c r="C19" s="16" t="n"/>
-      <c r="D19" s="16" t="n"/>
-      <c r="E19" s="16" t="n"/>
-      <c r="F19" s="16" t="n"/>
-      <c r="G19" s="10">
+      <c r="A19" s="15" t="n"/>
+      <c r="B19" s="15" t="n"/>
+      <c r="C19" s="15" t="n"/>
+      <c r="D19" s="15" t="n"/>
+      <c r="E19" s="15" t="n"/>
+      <c r="F19" s="15" t="n"/>
+      <c r="G19" s="8">
         <f>IF(COUNTA(A19)=0,"",IF(COUNTIF(B19:F19,"A")=1,"OK",IF(COUNTIF(B19:F19,"A")=0,"NO OWNER","MORE THAN ONE")))</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="16" t="n"/>
-      <c r="B20" s="16" t="n"/>
-      <c r="C20" s="16" t="n"/>
-      <c r="D20" s="16" t="n"/>
-      <c r="E20" s="16" t="n"/>
-      <c r="F20" s="16" t="n"/>
-      <c r="G20" s="10">
+      <c r="A20" s="15" t="n"/>
+      <c r="B20" s="15" t="n"/>
+      <c r="C20" s="15" t="n"/>
+      <c r="D20" s="15" t="n"/>
+      <c r="E20" s="15" t="n"/>
+      <c r="F20" s="15" t="n"/>
+      <c r="G20" s="8">
         <f>IF(COUNTA(A20)=0,"",IF(COUNTIF(B20:F20,"A")=1,"OK",IF(COUNTIF(B20:F20,"A")=0,"NO OWNER","MORE THAN ONE")))</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="16" t="n"/>
-      <c r="B21" s="16" t="n"/>
-      <c r="C21" s="16" t="n"/>
-      <c r="D21" s="16" t="n"/>
-      <c r="E21" s="16" t="n"/>
-      <c r="F21" s="16" t="n"/>
-      <c r="G21" s="10">
+      <c r="A21" s="15" t="n"/>
+      <c r="B21" s="15" t="n"/>
+      <c r="C21" s="15" t="n"/>
+      <c r="D21" s="15" t="n"/>
+      <c r="E21" s="15" t="n"/>
+      <c r="F21" s="15" t="n"/>
+      <c r="G21" s="8">
         <f>IF(COUNTA(A21)=0,"",IF(COUNTIF(B21:F21,"A")=1,"OK",IF(COUNTIF(B21:F21,"A")=0,"NO OWNER","MORE THAN ONE")))</f>
         <v/>
       </c>

--- a/templates/22-stakeholder-and-raci.xlsx
+++ b/templates/22-stakeholder-and-raci.xlsx
@@ -1463,10 +1463,13 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="24" customHeight="1">
+    <row r="3" ht="48" customHeight="1">
       <c r="A3" s="13" t="inlineStr">
         <is>
-          <t>Key: Black Belt = the person running the project day to day · Champion = the executive who owns the problem and clears the obstacles · WFM = Workforce Management, the team that owns schedules and headcount</t>
+          <t>Key:
+• Black Belt = the person running the project day to day
+• Champion = the executive who owns the problem and clears the obstacles
+• WFM = Workforce Management, the team that owns schedules and headcount</t>
         </is>
       </c>
     </row>

--- a/templates/22-stakeholder-and-raci.xlsx
+++ b/templates/22-stakeholder-and-raci.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -52,6 +52,11 @@
     </font>
     <font>
       <sz val="11"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="FF4B5563"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="8">
@@ -109,7 +114,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -133,6 +138,9 @@
     <xf numFmtId="0" fontId="5" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -417,7 +425,7 @@
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>13</col>
+      <col>15</col>
       <colOff>0</colOff>
       <row>2</row>
       <rowOff>0</rowOff>
@@ -861,7 +869,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L28"/>
+  <dimension ref="A1:V28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -875,6 +883,15 @@
     <col width="6" customWidth="1" min="10" max="10"/>
     <col width="6" customWidth="1" min="11" max="11"/>
     <col width="6" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
+    <col width="13" customWidth="1" min="19" max="19"/>
+    <col width="13" customWidth="1" min="20" max="20"/>
+    <col width="13" customWidth="1" min="21" max="21"/>
+    <col width="13" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -1366,7 +1383,7 @@
       <c r="F25" s="11" t="n"/>
       <c r="G25" s="11" t="n"/>
     </row>
-    <row r="26">
+    <row r="26" ht="66" customHeight="1">
       <c r="A26" s="12" t="inlineStr">
         <is>
           <t>Stakeholders mapped</t>
@@ -1376,6 +1393,12 @@
         <f>COUNTA(A5:A23)</f>
         <v/>
       </c>
+      <c r="N26" s="13" t="inlineStr">
+        <is>
+          <t>HOW TO READ IT.  Position is what matters, not the dots. High influence with low support is the quadrant that kills projects, and it is the one people leave until last. Anyone up and to the left needs a named plan and a date before Improve starts.
+SO:  Name an owner and a date for everyone in the high-influence, low-support quadrant, and do it before Improve. That quadrant does not resolve itself and it decides the project.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
@@ -1400,9 +1423,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="7">
     <mergeCell ref="A27:D27"/>
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="N26:V26"/>
     <mergeCell ref="A26:D26"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A25:G25"/>
@@ -1464,7 +1488,7 @@
       </c>
     </row>
     <row r="3" ht="48" customHeight="1">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>Key:
 • Black Belt = the person running the project day to day
@@ -1511,32 +1535,32 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="14" t="inlineStr">
+      <c r="A5" s="15" t="inlineStr">
         <is>
           <t>Sign the benefit and harvest mechanism</t>
         </is>
       </c>
-      <c r="B5" s="14" t="inlineStr">
+      <c r="B5" s="15" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="C5" s="14" t="inlineStr">
+      <c r="C5" s="15" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="D5" s="14" t="inlineStr">
+      <c r="D5" s="15" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="E5" s="14" t="inlineStr">
+      <c r="E5" s="15" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="F5" s="14" t="inlineStr">
+      <c r="F5" s="15" t="inlineStr">
         <is>
           <t>R</t>
         </is>
@@ -1547,32 +1571,32 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="14" t="inlineStr">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>Agree the operational definition of a defect</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B6" s="15" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="C6" s="14" t="inlineStr">
+      <c r="C6" s="15" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="D6" s="14" t="inlineStr">
+      <c r="D6" s="15" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="E6" s="14" t="inlineStr">
+      <c r="E6" s="15" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="F6" s="14" t="inlineStr">
+      <c r="F6" s="15" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -1583,32 +1607,32 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="14" t="inlineStr">
+      <c r="A7" s="15" t="inlineStr">
         <is>
           <t>Approve the pilot design and stopping rule</t>
         </is>
       </c>
-      <c r="B7" s="14" t="inlineStr">
+      <c r="B7" s="15" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="C7" s="14" t="inlineStr">
+      <c r="C7" s="15" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="D7" s="14" t="inlineStr">
+      <c r="D7" s="15" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="E7" s="14" t="inlineStr">
+      <c r="E7" s="15" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="F7" s="14" t="inlineStr">
+      <c r="F7" s="15" t="inlineStr">
         <is>
           <t>I</t>
         </is>
@@ -1619,32 +1643,32 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="14" t="inlineStr">
+      <c r="A8" s="15" t="inlineStr">
         <is>
           <t>Change the routing rules in production</t>
         </is>
       </c>
-      <c r="B8" s="14" t="inlineStr">
+      <c r="B8" s="15" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="C8" s="14" t="inlineStr">
+      <c r="C8" s="15" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="D8" s="14" t="inlineStr">
+      <c r="D8" s="15" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="E8" s="14" t="inlineStr">
+      <c r="E8" s="15" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="F8" s="14" t="inlineStr">
+      <c r="F8" s="15" t="inlineStr">
         <is>
           <t>I</t>
         </is>
@@ -1655,32 +1679,32 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="14" t="inlineStr">
+      <c r="A9" s="15" t="inlineStr">
         <is>
           <t>Own the control chart and its reaction plan</t>
         </is>
       </c>
-      <c r="B9" s="14" t="inlineStr">
+      <c r="B9" s="15" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="C9" s="14" t="inlineStr">
+      <c r="C9" s="15" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="D9" s="14" t="inlineStr">
+      <c r="D9" s="15" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="E9" s="14" t="inlineStr">
+      <c r="E9" s="15" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="F9" s="14" t="inlineStr">
+      <c r="F9" s="15" t="inlineStr">
         <is>
           <t>I</t>
         </is>
@@ -1691,32 +1715,32 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="14" t="inlineStr">
+      <c r="A10" s="15" t="inlineStr">
         <is>
           <t>Release the headcount the project frees</t>
         </is>
       </c>
-      <c r="B10" s="14" t="inlineStr">
+      <c r="B10" s="15" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="C10" s="14" t="inlineStr">
+      <c r="C10" s="15" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D10" s="14" t="inlineStr">
+      <c r="D10" s="15" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="E10" s="14" t="inlineStr">
+      <c r="E10" s="15" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="F10" s="14" t="inlineStr">
+      <c r="F10" s="15" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -1727,132 +1751,132 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="15" t="n"/>
-      <c r="B11" s="15" t="n"/>
-      <c r="C11" s="15" t="n"/>
-      <c r="D11" s="15" t="n"/>
-      <c r="E11" s="15" t="n"/>
-      <c r="F11" s="15" t="n"/>
+      <c r="A11" s="16" t="n"/>
+      <c r="B11" s="16" t="n"/>
+      <c r="C11" s="16" t="n"/>
+      <c r="D11" s="16" t="n"/>
+      <c r="E11" s="16" t="n"/>
+      <c r="F11" s="16" t="n"/>
       <c r="G11" s="8">
         <f>IF(COUNTA(A11)=0,"",IF(COUNTIF(B11:F11,"A")=1,"OK",IF(COUNTIF(B11:F11,"A")=0,"NO OWNER","MORE THAN ONE")))</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="n"/>
-      <c r="B12" s="15" t="n"/>
-      <c r="C12" s="15" t="n"/>
-      <c r="D12" s="15" t="n"/>
-      <c r="E12" s="15" t="n"/>
-      <c r="F12" s="15" t="n"/>
+      <c r="A12" s="16" t="n"/>
+      <c r="B12" s="16" t="n"/>
+      <c r="C12" s="16" t="n"/>
+      <c r="D12" s="16" t="n"/>
+      <c r="E12" s="16" t="n"/>
+      <c r="F12" s="16" t="n"/>
       <c r="G12" s="8">
         <f>IF(COUNTA(A12)=0,"",IF(COUNTIF(B12:F12,"A")=1,"OK",IF(COUNTIF(B12:F12,"A")=0,"NO OWNER","MORE THAN ONE")))</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="n"/>
-      <c r="B13" s="15" t="n"/>
-      <c r="C13" s="15" t="n"/>
-      <c r="D13" s="15" t="n"/>
-      <c r="E13" s="15" t="n"/>
-      <c r="F13" s="15" t="n"/>
+      <c r="A13" s="16" t="n"/>
+      <c r="B13" s="16" t="n"/>
+      <c r="C13" s="16" t="n"/>
+      <c r="D13" s="16" t="n"/>
+      <c r="E13" s="16" t="n"/>
+      <c r="F13" s="16" t="n"/>
       <c r="G13" s="8">
         <f>IF(COUNTA(A13)=0,"",IF(COUNTIF(B13:F13,"A")=1,"OK",IF(COUNTIF(B13:F13,"A")=0,"NO OWNER","MORE THAN ONE")))</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="15" t="n"/>
-      <c r="B14" s="15" t="n"/>
-      <c r="C14" s="15" t="n"/>
-      <c r="D14" s="15" t="n"/>
-      <c r="E14" s="15" t="n"/>
-      <c r="F14" s="15" t="n"/>
+      <c r="A14" s="16" t="n"/>
+      <c r="B14" s="16" t="n"/>
+      <c r="C14" s="16" t="n"/>
+      <c r="D14" s="16" t="n"/>
+      <c r="E14" s="16" t="n"/>
+      <c r="F14" s="16" t="n"/>
       <c r="G14" s="8">
         <f>IF(COUNTA(A14)=0,"",IF(COUNTIF(B14:F14,"A")=1,"OK",IF(COUNTIF(B14:F14,"A")=0,"NO OWNER","MORE THAN ONE")))</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="15" t="n"/>
-      <c r="B15" s="15" t="n"/>
-      <c r="C15" s="15" t="n"/>
-      <c r="D15" s="15" t="n"/>
-      <c r="E15" s="15" t="n"/>
-      <c r="F15" s="15" t="n"/>
+      <c r="A15" s="16" t="n"/>
+      <c r="B15" s="16" t="n"/>
+      <c r="C15" s="16" t="n"/>
+      <c r="D15" s="16" t="n"/>
+      <c r="E15" s="16" t="n"/>
+      <c r="F15" s="16" t="n"/>
       <c r="G15" s="8">
         <f>IF(COUNTA(A15)=0,"",IF(COUNTIF(B15:F15,"A")=1,"OK",IF(COUNTIF(B15:F15,"A")=0,"NO OWNER","MORE THAN ONE")))</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="15" t="n"/>
-      <c r="B16" s="15" t="n"/>
-      <c r="C16" s="15" t="n"/>
-      <c r="D16" s="15" t="n"/>
-      <c r="E16" s="15" t="n"/>
-      <c r="F16" s="15" t="n"/>
+      <c r="A16" s="16" t="n"/>
+      <c r="B16" s="16" t="n"/>
+      <c r="C16" s="16" t="n"/>
+      <c r="D16" s="16" t="n"/>
+      <c r="E16" s="16" t="n"/>
+      <c r="F16" s="16" t="n"/>
       <c r="G16" s="8">
         <f>IF(COUNTA(A16)=0,"",IF(COUNTIF(B16:F16,"A")=1,"OK",IF(COUNTIF(B16:F16,"A")=0,"NO OWNER","MORE THAN ONE")))</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="n"/>
-      <c r="B17" s="15" t="n"/>
-      <c r="C17" s="15" t="n"/>
-      <c r="D17" s="15" t="n"/>
-      <c r="E17" s="15" t="n"/>
-      <c r="F17" s="15" t="n"/>
+      <c r="A17" s="16" t="n"/>
+      <c r="B17" s="16" t="n"/>
+      <c r="C17" s="16" t="n"/>
+      <c r="D17" s="16" t="n"/>
+      <c r="E17" s="16" t="n"/>
+      <c r="F17" s="16" t="n"/>
       <c r="G17" s="8">
         <f>IF(COUNTA(A17)=0,"",IF(COUNTIF(B17:F17,"A")=1,"OK",IF(COUNTIF(B17:F17,"A")=0,"NO OWNER","MORE THAN ONE")))</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="15" t="n"/>
-      <c r="B18" s="15" t="n"/>
-      <c r="C18" s="15" t="n"/>
-      <c r="D18" s="15" t="n"/>
-      <c r="E18" s="15" t="n"/>
-      <c r="F18" s="15" t="n"/>
+      <c r="A18" s="16" t="n"/>
+      <c r="B18" s="16" t="n"/>
+      <c r="C18" s="16" t="n"/>
+      <c r="D18" s="16" t="n"/>
+      <c r="E18" s="16" t="n"/>
+      <c r="F18" s="16" t="n"/>
       <c r="G18" s="8">
         <f>IF(COUNTA(A18)=0,"",IF(COUNTIF(B18:F18,"A")=1,"OK",IF(COUNTIF(B18:F18,"A")=0,"NO OWNER","MORE THAN ONE")))</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="15" t="n"/>
-      <c r="B19" s="15" t="n"/>
-      <c r="C19" s="15" t="n"/>
-      <c r="D19" s="15" t="n"/>
-      <c r="E19" s="15" t="n"/>
-      <c r="F19" s="15" t="n"/>
+      <c r="A19" s="16" t="n"/>
+      <c r="B19" s="16" t="n"/>
+      <c r="C19" s="16" t="n"/>
+      <c r="D19" s="16" t="n"/>
+      <c r="E19" s="16" t="n"/>
+      <c r="F19" s="16" t="n"/>
       <c r="G19" s="8">
         <f>IF(COUNTA(A19)=0,"",IF(COUNTIF(B19:F19,"A")=1,"OK",IF(COUNTIF(B19:F19,"A")=0,"NO OWNER","MORE THAN ONE")))</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="15" t="n"/>
-      <c r="B20" s="15" t="n"/>
-      <c r="C20" s="15" t="n"/>
-      <c r="D20" s="15" t="n"/>
-      <c r="E20" s="15" t="n"/>
-      <c r="F20" s="15" t="n"/>
+      <c r="A20" s="16" t="n"/>
+      <c r="B20" s="16" t="n"/>
+      <c r="C20" s="16" t="n"/>
+      <c r="D20" s="16" t="n"/>
+      <c r="E20" s="16" t="n"/>
+      <c r="F20" s="16" t="n"/>
       <c r="G20" s="8">
         <f>IF(COUNTA(A20)=0,"",IF(COUNTIF(B20:F20,"A")=1,"OK",IF(COUNTIF(B20:F20,"A")=0,"NO OWNER","MORE THAN ONE")))</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="15" t="n"/>
-      <c r="B21" s="15" t="n"/>
-      <c r="C21" s="15" t="n"/>
-      <c r="D21" s="15" t="n"/>
-      <c r="E21" s="15" t="n"/>
-      <c r="F21" s="15" t="n"/>
+      <c r="A21" s="16" t="n"/>
+      <c r="B21" s="16" t="n"/>
+      <c r="C21" s="16" t="n"/>
+      <c r="D21" s="16" t="n"/>
+      <c r="E21" s="16" t="n"/>
+      <c r="F21" s="16" t="n"/>
       <c r="G21" s="8">
         <f>IF(COUNTA(A21)=0,"",IF(COUNTIF(B21:F21,"A")=1,"OK",IF(COUNTIF(B21:F21,"A")=0,"NO OWNER","MORE THAN ONE")))</f>
         <v/>
